--- a/data/trans_orig/IP07A10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A10-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25496</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30739</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>46494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25696</t>
+          <t>25579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>28080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34944</t>
+          <t>35216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51055</t>
+          <t>50889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>20499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>45575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66438</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58638</t>
+          <t>60401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81338</t>
+          <t>83126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111063</t>
+          <t>110345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142922</t>
+          <t>140530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90814</t>
+          <t>90858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113937</t>
+          <t>113884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104439</t>
+          <t>103091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127262</t>
+          <t>128277</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>200443</t>
+          <t>202087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235320</t>
+          <t>235018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>33280</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51380</t>
+          <t>51365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40113</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60097</t>
+          <t>59240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77431</t>
+          <t>78016</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104646</t>
+          <t>104776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26579</t>
+          <t>25546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>44757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>22196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>35179</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51009</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69346</t>
+          <t>68956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>22718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20902</t>
+          <t>21160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36431</t>
+          <t>35824</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79527</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105804</t>
+          <t>106554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94390</t>
+          <t>95263</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121528</t>
+          <t>121789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181738</t>
+          <t>182594</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219024</t>
+          <t>218298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>139684</t>
+          <t>139917</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167770</t>
+          <t>168441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>152043</t>
+          <t>154098</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>182171</t>
+          <t>182596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>300277</t>
+          <t>301328</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>342436</t>
+          <t>341890</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56023</t>
+          <t>55413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81082</t>
+          <t>80147</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54556</t>
+          <t>55339</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>78063</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>117058</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149372</t>
+          <t>149016</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,42 +3173,42 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>6431</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>11317</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>1,7%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>11462</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30240</t>
+          <t>30003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>21858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49425</t>
+          <t>49097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,63%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>27881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>13062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>23465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31111</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47288</t>
+          <t>48557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>22033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62838</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86679</t>
+          <t>86325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84745</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109745</t>
+          <t>109706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154457</t>
+          <t>155386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187157</t>
+          <t>188978</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84675</t>
+          <t>84964</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108990</t>
+          <t>108987</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85484</t>
+          <t>85483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110245</t>
+          <t>109668</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177607</t>
+          <t>177267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210522</t>
+          <t>211421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>23217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40775</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22294</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38700</t>
+          <t>38514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49674</t>
+          <t>49991</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73972</t>
+          <t>74029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23511</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37028</t>
+          <t>37637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41968</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60122</t>
+          <t>60100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20966</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>34300</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>20167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31413</t>
+          <t>32726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43115</t>
+          <t>44600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62299</t>
+          <t>62842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19788</t>
+          <t>19739</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114333</t>
+          <t>115550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144334</t>
+          <t>144345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120177</t>
+          <t>120449</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150044</t>
+          <t>149008</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>241801</t>
+          <t>244473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282877</t>
+          <t>284061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132069</t>
+          <t>131654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>159882</t>
+          <t>161210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>126948</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155970</t>
+          <t>157559</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>267474</t>
+          <t>265998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>309716</t>
+          <t>307420</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>37855</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58264</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>76371</t>
+          <t>74989</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>105646</t>
+          <t>103894</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28759</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43322</t>
+          <t>42772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,48%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92511</t>
+          <t>92431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117855</t>
+          <t>118823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>86475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112220</t>
+          <t>111885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186196</t>
+          <t>186437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221709</t>
+          <t>222922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88491</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114763</t>
+          <t>115511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96755</t>
+          <t>98435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122381</t>
+          <t>124094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196231</t>
+          <t>192147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>230279</t>
+          <t>228657</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,05%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>26375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45705</t>
+          <t>44796</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39945</t>
+          <t>39095</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53430</t>
+          <t>53811</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78265</t>
+          <t>78224</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>18265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35065</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>42245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>52890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>72881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42644</t>
+          <t>42403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26389</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57870</t>
+          <t>58772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78552</t>
+          <t>80284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129212</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159040</t>
+          <t>160442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130224</t>
+          <t>131036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160981</t>
+          <t>160760</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>268850</t>
+          <t>268613</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>310988</t>
+          <t>311359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>140063</t>
+          <t>139372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>169803</t>
+          <t>169610</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>146957</t>
+          <t>146408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>178309</t>
+          <t>178404</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>294019</t>
+          <t>295945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>336572</t>
+          <t>341703</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>36615</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58222</t>
+          <t>57644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55314</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>76458</t>
+          <t>77435</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>105744</t>
+          <t>109312</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido disfrutar de su tiempo libre en 2023 (tasa de respuesta: 99,79%)</t>
+          <t>Menores según la frecuencia de haber podido disfrutar de su tiempo libre, percibida por el adulto en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25069</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>20746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28325</t>
+          <t>27394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>43333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100684</t>
+          <t>88705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164937</t>
+          <t>164101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167832</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208506</t>
+          <t>209834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280937</t>
+          <t>282027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>361118</t>
+          <t>362535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76813</t>
+          <t>77640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149100</t>
+          <t>155852</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80573</t>
+          <t>78562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117457</t>
+          <t>116579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168565</t>
+          <t>168238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252579</t>
+          <t>259698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>21216</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51516</t>
+          <t>49793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>416</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10764,77 +10764,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8364</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>4811</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>9538</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>889</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7858</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>4811</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>10300</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43630</t>
+          <t>42750</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58059</t>
+          <t>57166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60906</t>
+          <t>60817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79675</t>
+          <t>79955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109483</t>
+          <t>110515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133701</t>
+          <t>134083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>16398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>29851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35498</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>37216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60810</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15935</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11388,7 +11388,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167819</t>
+          <t>163831</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>238200</t>
+          <t>239073</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>253476</t>
+          <t>252924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298778</t>
+          <t>300237</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>438980</t>
+          <t>436115</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>527234</t>
+          <t>526584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105311</t>
+          <t>105616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183020</t>
+          <t>186935</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,82 +11784,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>134263</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>114526</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>157803</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>35,89%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>263567</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>230694</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>325796</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>28,51%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>49,55%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>134263</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>114487</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>158597</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>36,07%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>263567</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>230908</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>328086</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>32,58%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
